--- a/05_Figures/F06_prediction/proteins/T2/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/d_1rm_legpress/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,454 +131,478 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">ANKRD2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRKAR2A</t>
   </si>
   <si>
+    <t xml:space="preserve">RPLP0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHSA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAD3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDHA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIP4K2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YBX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERMT2</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCCC2</t>
   </si>
   <si>
-    <t xml:space="preserve">RPLP0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHSA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKRD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAD3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL19</t>
+    <t xml:space="preserve">MRPS22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUTF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13</t>
   </si>
   <si>
     <t xml:space="preserve">RPL7A</t>
   </si>
   <si>
-    <t xml:space="preserve">YBX1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADSL</t>
   </si>
   <si>
-    <t xml:space="preserve">ANXA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERMT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUTF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDHA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIP4K2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTB</t>
-  </si>
-  <si>
     <t xml:space="preserve">EIF3F</t>
   </si>
   <si>
     <t xml:space="preserve">PARP1</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL13</t>
+    <t xml:space="preserve">RPS6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMM50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG1</t>
   </si>
   <si>
     <t xml:space="preserve">CHP1</t>
   </si>
   <si>
-    <t xml:space="preserve">RPS6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMM50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG1</t>
+    <t xml:space="preserve">OGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCN1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX5B</t>
   </si>
   <si>
     <t xml:space="preserve">CRADD</t>
   </si>
   <si>
-    <t xml:space="preserve">EHD2</t>
+    <t xml:space="preserve">DDB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATXN10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPEG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX19A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSK3B</t>
   </si>
   <si>
     <t xml:space="preserve">IBA57</t>
   </si>
   <si>
-    <t xml:space="preserve">SCN1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDB1</t>
+    <t xml:space="preserve">IMMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL23A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCUN1D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGIC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAMPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKG1</t>
   </si>
   <si>
     <t xml:space="preserve">PITHD1</t>
   </si>
   <si>
-    <t xml:space="preserve">SPEG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL23A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATXN10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCUN1D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX19A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGIC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPST</t>
+    <t xml:space="preserve">RPLP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELENBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLMAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UROD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APMAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL6IP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCAP29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDH13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX4I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX6B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSE1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL4A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGLUCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1I2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERP44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORASP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPNA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAVS</t>
   </si>
   <si>
     <t xml:space="preserve">MRPS16</t>
   </si>
   <si>
-    <t xml:space="preserve">NACA</t>
+    <t xml:space="preserve">MRPS28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLRX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBSCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R5D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAP1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL10A</t>
   </si>
   <si>
     <t xml:space="preserve">RPL14</t>
   </si>
   <si>
-    <t xml:space="preserve">RPS13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENBP1</t>
+    <t xml:space="preserve">RPL5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SESN1</t>
   </si>
   <si>
     <t xml:space="preserve">SIRT5</t>
   </si>
   <si>
-    <t xml:space="preserve">SLMAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TECR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCAP29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX4I1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX6B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSE1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL4A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGLUCY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1I2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERP44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FGGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSK3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTRES1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NLRX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBSCN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKLR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R5D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAP1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDH13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAR1B</t>
+    <t xml:space="preserve">SKP1</t>
   </si>
   <si>
     <t xml:space="preserve">SLC25A20</t>
@@ -596,7 +620,7 @@
     <t xml:space="preserve">TMED10</t>
   </si>
   <si>
-    <t xml:space="preserve">TMED5</t>
+    <t xml:space="preserve">UFM1</t>
   </si>
   <si>
     <t xml:space="preserve">UQCC3</t>
@@ -995,16 +1019,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.59554019980348</v>
+        <v>-1.28564022645393</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.403591501875474</v>
+        <v>-0.475341102208891</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1028,29 +1052,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.59554019980348</v>
+        <v>-1.28564022645393</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.403591501875474</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.45273631840796</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.741293532338308</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.691660874919098</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.662903562654804</v>
-      </c>
+        <v>-0.475341102208891</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1074,2206 +1090,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.03691870144274</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.10214321367869</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.205659938004264</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.712872968504528</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.995102272405837</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.679141103740718</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.159932127290878</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.42964492348863</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.306989232659326</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.865691252592384</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.7051732445315</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-1.34794757472847</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.410042239682659</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.03098175681765</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.0474711652883502</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.02523227765163</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.17843455812186</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.177344913163112</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.698280304967895</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.830813490854883</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.67823233054795</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.777872938730603</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.00873674892891</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.884698336872632</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.540359119404569</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.700228129127405</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.467620909956699</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.177579772746444</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.105637120322292</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.901524657753223</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.0686985209956236</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.392940058890722</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.60315459434097</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.26095253943242</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.0684270978935524</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.0180674623001809</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-2.00209241399745</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.10443904131684</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.2462629101136</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.97870505153192</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.25575737128197</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.977411476114874</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.353216878064302</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-1.68032981683836</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.212433206581386</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.171756072732548</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-1.37175491963649</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0328044305216554</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.774013830930946</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.419837602622378</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.88455978210172</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.917613662798936</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.113011698376144</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.81545487152614</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.198701441292378</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.220746164866722</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.961108502133162</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.286792614637062</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.703212024276267</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.95851287793799</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-1.35225991621439</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.4504741115453</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.131019106660205</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.00120105147854</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.26735771262043</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.261980912335382</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.550526148833372</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.64159551879553</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.301891608908081</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.05503568790009</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-1.80714406671989</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.46832213559829</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.19159903831164</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-1.03398394740477</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.55389882863678</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.517242446735804</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.527991523492567</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.139287118521</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.23834421187145</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.843912791501754</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.52529752775412</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.95040226307464</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.435053118747585</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.723184684658358</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.93389146424923</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.915742288987146</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.826115634120522</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.375595644767756</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.46611466102324</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.106272536027638</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.530456698995829</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.0294771824865148</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.417703287379356</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.62938566476313</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.895583481475662</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.22714006436927</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.604885640991412</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.207373559256497</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.553885166850559</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.857166063426231</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.432718980107711</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.572043629506041</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.316785821039538</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.377564604868725</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.377228583958463</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-2.05376652568989</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-2.25774489750884</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.726493861710021</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.489953352617158</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.58381032185063</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.25387535921083</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-1.00271007604849</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.019472514723998</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.0318846271997071</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.21939175905649</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.13408187123902</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-1.16807133134984</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.244494406840262</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-2.6847343309294</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.0269051614741733</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.90211322728629</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0.384152166262496</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.675748493548869</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-1.95292484401391</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-2.55082021405665</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0.370990586950059</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.683429552328557</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.997790664650476</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.477161888251992</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.360503367240815</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.60168892982017</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.607572222734612</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.659150366513176</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.185765045244475</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.248730349198925</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.488827418166014</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0.340043637162572</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.550219019552127</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.294135058397966</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.351074284976782</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.386597782481258</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.881187567071857</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.493399138133895</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.370961155542433</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.14174735306924</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.367019731284357</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.29460317096466</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.23803642846348</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.90313667251706</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.173518107750049</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.703936434257438</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.413259038189771</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-2.20918618469802</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0.00224464280423031</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.03471821271958</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.38756556344816</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.367451035693436</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.333817763359681</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-1.03672509660458</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.982730389334856</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.713294965875881</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.618642607361869</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.128406571336236</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.891092150842589</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.588765748771256</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.647522763271005</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-1.1784745001815</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.970187608151778</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.426663421381255</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.77429029667172</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.0764381450587748</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-2.513269464027</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.265466239575707</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-1.98401054645137</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.184724850256346</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>0.261991489758758</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.556557935571937</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.11730370977058</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.901368654812956</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.607584721842808</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.296485427855818</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.482126382076381</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.209177753762949</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.265175459326641</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.11432307267413</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.885420777074495</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.301025581915661</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-1.22132841200038</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.505838686008365</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.769635820312332</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.9261178201535</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>0.300512118701928</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.904937543274967</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.142281289085768</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.084551949248928</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.90565738272523</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.395538220861967</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.454362751832341</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.021586639876868</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.64622865029758</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3316,7 +1132,7 @@
         <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>43.108484174448</v>
+        <v>40.9152381737149</v>
       </c>
     </row>
     <row r="3">
@@ -3333,7 +1149,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>37.3499570391923</v>
+        <v>35.5212652994738</v>
       </c>
     </row>
     <row r="4">
@@ -3350,7 +1166,7 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>32.640808753799</v>
+        <v>31.0876124244674</v>
       </c>
     </row>
     <row r="5">
@@ -3367,7 +1183,7 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>47.3898102237754</v>
+        <v>44.2615834656338</v>
       </c>
     </row>
     <row r="6">
@@ -3384,7 +1200,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>46.1854579208841</v>
+        <v>53.900848260558</v>
       </c>
     </row>
     <row r="7">
@@ -3401,7 +1217,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>39.9326039717472</v>
+        <v>45.8195859365009</v>
       </c>
     </row>
     <row r="8">
@@ -3418,7 +1234,7 @@
         <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>49.412810657422</v>
+        <v>50.2738265806911</v>
       </c>
     </row>
     <row r="9">
@@ -3435,7 +1251,7 @@
         <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>24.5878276877812</v>
+        <v>24.6061184607188</v>
       </c>
     </row>
     <row r="10">
@@ -3452,7 +1268,7 @@
         <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>50.2411581130726</v>
+        <v>46.327720257362</v>
       </c>
     </row>
     <row r="11">
@@ -3469,7 +1285,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>54.8024750553928</v>
+        <v>43.0818038620609</v>
       </c>
     </row>
     <row r="12">
@@ -3486,7 +1302,7 @@
         <v>62</v>
       </c>
       <c r="E12" t="n">
-        <v>47.9823733457798</v>
+        <v>45.5598145912103</v>
       </c>
     </row>
     <row r="13">
@@ -3503,7 +1319,7 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.5154339810313</v>
+        <v>-15.6587329337215</v>
       </c>
     </row>
     <row r="14">
@@ -3520,7 +1336,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>24.2336337239391</v>
+        <v>-80.3851508000282</v>
       </c>
     </row>
     <row r="15">
@@ -3537,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>54.9918013787038</v>
+        <v>53.8763342561662</v>
       </c>
     </row>
     <row r="16">
@@ -3554,7 +1370,7 @@
         <v>89</v>
       </c>
       <c r="E16" t="n">
-        <v>21.330213773608</v>
+        <v>20.9799122560015</v>
       </c>
     </row>
   </sheetData>
@@ -3596,10 +1412,10 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3664,10 +1480,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.933333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -3715,10 +1531,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.866666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -3732,10 +1548,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.866666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -3749,10 +1565,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.866666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -4004,10 +1820,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0.733333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -4021,10 +1837,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0.733333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -4072,10 +1888,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31">
@@ -4208,10 +2024,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -4225,10 +2041,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -4293,10 +2109,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -4310,10 +2126,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -4361,10 +2177,10 @@
         <v>83</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -4463,10 +2279,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -4616,10 +2432,10 @@
         <v>98</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63">
@@ -4633,10 +2449,10 @@
         <v>99</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
@@ -4650,10 +2466,10 @@
         <v>100</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="65">
@@ -4956,10 +2772,10 @@
         <v>118</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -6302,6 +4118,142 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="s">
+        <v>198</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="s">
+        <v>199</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>200</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="s">
+        <v>201</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="s">
+        <v>202</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="s">
+        <v>203</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="s">
+        <v>204</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="s">
+        <v>205</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T2/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/d_1rm_legpress/spls/c_data/results.xlsx
@@ -1055,7 +1055,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.28564022645393</v>
@@ -1063,10 +1063,18 @@
       <c r="I3" t="n">
         <v>-0.475341102208891</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.860696517412935</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.791044776119403</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.679101257369722</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.640654841218546</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1090,6 +1098,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.110006262798</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.14024954197511</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.209235326903522</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.745998019781204</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.985746085566652</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.889527811681324</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.177796989671372</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.48777301689219</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.23732511606765</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.91403586689022</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.359467979243989</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.42883942777212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.316250352068749</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.942018022232051</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.0796416504907489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.893344673675837</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.20198918545568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.158584321279206</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.838716439101477</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.867513176222801</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.7840896725197</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.276656182352748</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.19486149324829</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.666694206946524</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.623778466459648</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.535588538776298</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.390579238049823</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.471161163254094</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.0699517696816727</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.904086617113736</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.082463126783959</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.480241376143602</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.91184397142947</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.28182664193098</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.120568354913026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.231006579555489</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.88324463764472</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.24518196223259</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.10515880226679</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-2.05574359519361</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.11055312117289</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.711215134029267</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.688840409521302</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.39857440361875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.274041081986929</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.272105493507686</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-1.32533270021651</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0344023363970234</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.12538374698846</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.383615278589741</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.41386308920423</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.879556952268673</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.198345516877423</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.605074092369387</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.333376485607807</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.199783187763813</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.03061784028782</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.264069445443243</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.03805027865368</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.838506209395087</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.23379856230602</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.05157552315068</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.123271295277451</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.15489515190637</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.42834545591377</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.284014684928057</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.477773681605465</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.827043550200224</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.345675608711971</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.12084428659376</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.80128105056169</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.50137731895887</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.31808977661922</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.345542664084914</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.56751737655001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.532315074462119</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.48680156669396</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.17765971438854</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.16845024847896</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.13287111134995</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.64752136620608</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.863218036467237</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.42773055005576</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.70742894823554</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.08591761356586</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.696994548115207</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.815170615469115</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.407740570381487</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.50121668952304</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.0367588199122475</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.459016617498708</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.023153324361708</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.373062802959988</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.664909480575264</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.797813791441224</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.22562307097381</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.84280075563257</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.162691059202665</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.596253531184989</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.13616060896785</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.565787113038518</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.589144563039429</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.00151651411822384</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.377920773503451</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.314854466062121</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.54772545691767</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-2.55572484293494</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.866699328741784</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.515905803944796</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.65029950575962</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.598288418314638</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.14043426580697</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.00875143023228997</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.167720061945262</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.17046818484309</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.09515750077997</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.15451313120432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.0489357483946447</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-2.28254916196943</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.0512084762608163</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.93555529732826</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.405005131166788</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.725773267047536</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.54166755388446</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-2.04341822783202</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.384161264751428</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.661758018070847</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.961752032977992</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.564911149328911</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.352693030520765</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.61467390719958</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.583761514453439</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.752729925911908</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.229385296904517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.264570746405618</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.829496130056962</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.324051512176264</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.324640869916328</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.292332892955213</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.243862818592745</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.197517399678233</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.934396518403242</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.4775080023947</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.193838719870676</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.13327759993757</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.659352595227426</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.32140360890065</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.09992848111767</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.773169416427072</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.148187068337115</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.03001894482577</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.389074818807802</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-2.12224990861853</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.0454448196444965</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.986486459424838</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.603532692546028</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.245814965899239</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.0497002045249504</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.98478991864893</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.983406080464456</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.670815434072727</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.53342389771101</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.08015048622584</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.864297831800986</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.49786602415411</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.713744574070686</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.889039635916869</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.07743939403918</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.366163360794903</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.776370166974162</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.050808482606377</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-2.65569593657185</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.302882957484941</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-1.8578072739884</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.836643658094662</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.250277751447731</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.692787103186252</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.06395892388792</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.997296618767659</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.638559239236334</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.67870054343932</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.396193905908989</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.20558198378409</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.0902001240049856</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.982049279116287</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.809447134101482</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.16522124363618</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-1.04547009321957</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.469915376439185</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.781217822345722</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.732014039855358</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.359494041031258</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.13480038727449</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.148478893185374</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.10919437657896</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.27331054436135</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.292735335036363</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.469117761596813</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.0373982537356889</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.22644139501366</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
